--- a/data/trans_camb/P19C08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,73</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,4</t>
+          <t>-0,63; 0,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,6</t>
+          <t>-0,2; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,82</t>
+          <t>-0,18; 1,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,92</t>
+          <t>-0,69; 0,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,16</t>
+          <t>-1,0; 0,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,43</t>
+          <t>0,04; 1,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,48</t>
+          <t>-0,47; 0,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,63</t>
+          <t>-0,31; 0,64</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,88; —</t>
+          <t>-71,66; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,48; —</t>
+          <t>-29,04; 1308,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,54; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,29</t>
+          <t>-0,14; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,44</t>
+          <t>-0,26; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,09</t>
+          <t>-0,52; 0,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,73</t>
+          <t>-0,44; 0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,27</t>
+          <t>-0,86; 0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,23</t>
+          <t>-0,87; 0,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,74</t>
+          <t>-0,16; 0,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,1</t>
+          <t>-0,49; 0,09</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,89; 847,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,57</t>
+          <t>-0,53; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,29</t>
+          <t>-1,06; 0,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,97</t>
+          <t>-0,41; 2,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; -0,14</t>
+          <t>-1,42; -0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,89</t>
+          <t>-0,75; 0,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,72</t>
+          <t>-0,86; 0,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,53</t>
+          <t>-0,58; 0,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,35</t>
+          <t>-0,73; 0,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,96</t>
+          <t>-0,46; 0,98</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-81,81; 992,55</t>
+          <t>-80,37; 1049,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,02; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 472,31</t>
+          <t>-86,63; 541,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,38; 281,58</t>
+          <t>-76,86; 343,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,77; 280,65</t>
+          <t>-100,0; 271,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 357,02</t>
+          <t>-60,55; 445,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,44</t>
+          <t>-0,9; 0,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,14</t>
+          <t>-1,02; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,39</t>
+          <t>-0,89; 0,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,81</t>
+          <t>-1,04; 0,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,37</t>
+          <t>-1,84; -0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,35</t>
+          <t>-1,26; 0,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,42</t>
+          <t>-0,71; 0,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; -0,3</t>
+          <t>-1,2; -0,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,2</t>
+          <t>-0,86; 0,22</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 374,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,49; —</t>
+          <t>-94,38; inf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 211,61</t>
+          <t>-71,03; 178,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 95,69</t>
+          <t>-82,0; 114,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,39; 112,17</t>
+          <t>-65,75; 113,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,17</t>
+          <t>-100,0; -14,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 54,37</t>
+          <t>-75,71; 58,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,76</t>
+          <t>-0,1; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,08</t>
+          <t>-0,48; 0,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,5</t>
+          <t>-0,2; 0,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,47</t>
+          <t>-0,33; 0,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; -0,02</t>
+          <t>-0,7; 0,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,16</t>
+          <t>-0,55; 0,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,45</t>
+          <t>-0,13; 0,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; -0,05</t>
+          <t>-0,52; -0,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,21</t>
+          <t>-0,28; 0,21</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 394,86</t>
+          <t>-26,28; 324,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,62; 58,92</t>
+          <t>-87,75; 71,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 280,4</t>
+          <t>-45,72; 263,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 130,68</t>
+          <t>-44,4; 144,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 5,38</t>
+          <t>-89,02; 18,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 49,69</t>
+          <t>-67,82; 47,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 137,44</t>
+          <t>-23,38; 149,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-83,67; -10,35</t>
+          <t>-84,12; -5,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 65,62</t>
+          <t>-48,33; 64,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>-0,13; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,44</t>
+          <t>-0,21; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,97</t>
+          <t>-0,27; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,83</t>
+          <t>-0,71; 0,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,15</t>
+          <t>-1,01; 0,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,44</t>
+          <t>0,08; 1,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,46</t>
+          <t>-0,46; 0,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,64</t>
+          <t>-0,35; 0,57</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>247,81%</t>
+          <t>224,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-57,94%</t>
+          <t>-58,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,66; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 1308,46</t>
+          <t>-9,82; 1223,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,34; 664,03</t>
         </is>
       </c>
     </row>
@@ -850,37 +850,37 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,23</t>
+          <t>-0,14; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,56</t>
+          <t>-0,26; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,09</t>
+          <t>-0,52; 0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,81</t>
+          <t>-0,48; 0,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,14</t>
+          <t>-0,74; 0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,22</t>
+          <t>-0,73; 0,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,75</t>
+          <t>-0,17; 0,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,21</t>
+          <t>-0,41; 0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,09</t>
+          <t>-0,51; 0,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-66,12%</t>
+          <t>-57,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-35,76%</t>
+          <t>-36,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-49,78%</t>
+          <t>-43,54%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,65</t>
+          <t>-0,45; 1,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,37</t>
+          <t>-1,07; 0,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,25</t>
+          <t>-0,28; 2,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; -0,14</t>
+          <t>-1,43; -0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,97</t>
+          <t>-0,79; 0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,71</t>
+          <t>-0,54; 1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,6</t>
+          <t>-0,58; 0,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,39</t>
+          <t>-0,74; 0,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,98</t>
+          <t>-0,17; 1,38</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>137,22%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>106,48%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 1049,62</t>
+          <t>-70,35; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,02; —</t>
+          <t>-74,5; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,63; 541,49</t>
+          <t>-72,62; 643,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 343,72</t>
+          <t>-79,68; 340,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 271,43</t>
+          <t>-100,0; 229,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,55; 445,96</t>
+          <t>-37,47; 533,66</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,45</t>
+          <t>-0,87; 0,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,14</t>
+          <t>-1,01; 0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,43</t>
+          <t>-0,89; 0,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,83</t>
+          <t>-1,08; 0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; -0,37</t>
+          <t>-1,82; -0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,37</t>
+          <t>-1,28; 0,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,44</t>
+          <t>-0,73; 0,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; -0,25</t>
+          <t>-1,28; -0,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,22</t>
+          <t>-0,86; 0,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,41%</t>
+          <t>-28,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,57%</t>
+          <t>-37,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-36,35%</t>
+          <t>-35,12%</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,38; inf</t>
+          <t>-94,03; 341,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,03; 178,89</t>
+          <t>-71,74; 216,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,0; 114,14</t>
+          <t>-80,96; 78,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 113,86</t>
+          <t>-65,31; 113,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,02</t>
+          <t>-100,0; -46,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 58,48</t>
+          <t>-75,87; 69,82</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,68</t>
+          <t>-0,06; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,07</t>
+          <t>-0,49; 0,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,52</t>
+          <t>-0,16; 0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,48</t>
+          <t>-0,29; 0,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,01</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,14</t>
+          <t>-0,47; 0,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,46</t>
+          <t>-0,11; 0,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; -0,05</t>
+          <t>-0,5; -0,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,21</t>
+          <t>-0,2; 0,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-30,04%</t>
+          <t>-17,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 324,15</t>
+          <t>-22,48; 342,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 71,2</t>
+          <t>-91,41; 50,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 263,85</t>
+          <t>-36,82; 292,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 144,62</t>
+          <t>-42,55; 144,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-89,02; 18,05</t>
+          <t>-89,73; 17,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 47,09</t>
+          <t>-60,28; 71,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 149,22</t>
+          <t>-20,08; 149,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -5,29</t>
+          <t>-85,2; -15,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 64,82</t>
+          <t>-36,57; 104,59</t>
         </is>
       </c>
     </row>
